--- a/daily_matches/job_matches_2026-04-30.xlsx
+++ b/daily_matches/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Athena, Docker, Kubernetes, Git, Kafka, NoSQL, Python</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Athena, Docker, Kubernetes, Git, Kafka, NoSQL, Python</t>
+          <t>RAG, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Data Lake, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>Copilot, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=3188efd79bf1e92f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tunnl</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, PyTorch, XGBoost, Git, Snowflake, Databricks, Tableau, Matplotlib</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47947c9c1928b6</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Agentic Engineer</t>
+          <t>Senior Software Engineer (C#/SQL) - Plex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Mayfield Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e27d2766be790f</t>
+          <t>https://www.indeed.com/viewjob?jk=e79d1470a0b337d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Go)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VideoAmp</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>Redshift, Jenkins, Git, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40fa99bc27923a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4204825a3f07bee4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Redshift, Jenkins, Git, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=796d6aa417695ab4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - SLC</t>
+          <t>Senior Machine Learning Engineer, Content Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Solen Software Group</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, Python</t>
+          <t>Machine Learning Engineer, RAG, FAISS, Pinecone, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b06c7aed4161d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d276de9194c9c27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Sr. SDET (Senior Software Development Engineer in Test, Middleware)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=d03a534a15ff6662</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. SDET (Senior Software Development Engineer in Test, Middleware)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb4e9cb29fe1df7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d58a01f5c2560de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Growth AI</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, FastAPI, Docker, AKS, CI/CD, Git, Databricks, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,637 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418833ef95702c14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Generative AI Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0da976c95f354ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - MoneyLion</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Gen Digital Inc.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Knowledge Systems</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Justworks</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23b3c2cfa7f148e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Security Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>VideoAmp</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7234d2092e14cf17</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II - Automation</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Itential</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80989db114bfdfcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PAR Technology</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Git, Snowflake, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ccfc23b7ece84d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88385e70bf0d2e8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Research Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jack Henry &amp; Associates</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e05355245e692362</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>HYPER SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Tableau, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6cf2843671035af</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Junior Data Operations Development Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>California State University</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CI/CD, Snowflake, Databricks, Tableau, Quicksight, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f260e7e3d81d7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Engineering Business Analyst</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Alliance Laundry</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ripon, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Git, Snowflake, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19b17863daa1a5dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Xai</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Kubernetes, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab11fe5aabb5239</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Applied AI Engineering Intern</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>d-Matrix</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Git, Matplotlib, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31f3e6e263943a73</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Firefly Services</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dad38bf15350c24e</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Software Engineer II IS - Remote</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lubbock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84262d44b4801fdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b286602a0f4f00c</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e78c3f1d96fb2383</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec85dcfed7fba60</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9aa1d67dcf5a1a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-30.xlsx
+++ b/daily_matches/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,227 +468,227 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Gemini, S3, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Gemini, S3, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3188efd79bf1e92f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>HYBRID: Full-Stack x AI Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>SourceCo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, EC2, CI/CD, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b21c30af01c5b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/SQL) - Plex</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mayfield Heights, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79d1470a0b337d6</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, Jenkins, Git, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, CI/CD, Databricks, PySpark, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4204825a3f07bee4</t>
+          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Python - AI Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, Jenkins, Git, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796d6aa417695ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Content Engineering</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, FAISS, Pinecone, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d276de9194c9c27</t>
+          <t>https://www.indeed.com/viewjob?jk=19bc2fde31ea0812</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. SDET (Senior Software Development Engineer in Test, Middleware)</t>
+          <t>Mgr Software Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Synapse, Databricks, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03a534a15ff6662</t>
+          <t>https://www.indeed.com/viewjob?jk=a02d5f5b9c258176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. SDET (Senior Software Development Engineer in Test, Middleware)</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,52 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d58a01f5c2560de</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The AES Group</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9aa1d67dcf5a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3210fc5e11721889</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-30.xlsx
+++ b/daily_matches/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Gemini, S3, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc1848c21428ea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Database Reliability/Automation Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Gemini, S3, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=b651d1e6011934a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer (SQL, Python, Cloud)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB</t>
+          <t>Generative AI, S3, Glue, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HYBRID: Full-Stack x AI Automation Engineer</t>
+          <t>Clinical Data Scientist, Human Capital</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SourceCo</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, EC2, CI/CD, Git, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, RAG, PyTorch, Keras, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b21c30af01c5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe6028a2d83dae3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Autonomous Driving Vehicle Perception Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, YOLO, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=34e73d5c547b79e4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Research Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Databricks, PySpark, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=545a732106c8c6f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python - AI Platform</t>
+          <t>Engineer 2, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Redshift, Data Lake, Kubernetes, Git, Databricks, Redshift, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=a853581f988b1740</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bc2fde31ea0812</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mgr Software Engineering</t>
+          <t>Software Engineer - Sr Consultant level-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Synapse, Databricks, Power BI, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02d5f5b9c258176</t>
+          <t>https://www.indeed.com/viewjob?jk=23037e4495689aca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>AI NATIVE SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,122 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f4411f2f28fbbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APIM Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>American Electric Power</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f618d0ef272f7c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr. Net Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Matrix Precise Inc.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Berkeley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90fc26bc5e546ec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer I - IGEN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>U.S. Venture, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Appleton, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3210fc5e11721889</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43ad08d27434b10c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-30.xlsx
+++ b/daily_matches/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, CI/CD, Git, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc1848c21428ea</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Reliability/Automation Engineer</t>
+          <t>AI/ML Data Scientist (GPSSC)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b651d1e6011934a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c3733618642dbd3f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL, Python, Cloud)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Glue, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, S3, EC2, Redshift, Kinesis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=02ff0b4b24920c72</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clinical Data Scientist, Human Capital</t>
+          <t>Sr Engineer, AI Solutions</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHS Corporate</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, Keras, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe6028a2d83dae3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ffff09002cee6d4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Autonomous Driving Vehicle Perception Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, YOLO, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,137 +636,137 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e73d5c547b79e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Research Data Scientist</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Hypothesis Testing</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, EC2, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545a732106c8c6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer 2, Data &amp; Analytics</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Data Lake, Kubernetes, Git, Databricks, Redshift, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a853581f988b1740</t>
+          <t>https://www.indeed.com/viewjob?jk=9915fb51c50be337</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=098a368550354f0d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - Sr Consultant level-1</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, MLflow, Apache Airflow, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23037e4495689aca</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI NATIVE SOFTWARE ENGINEER</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f4411f2f28fbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APIM Platform Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f618d0ef272f7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=852eedab8ea16518</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Net Architect</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Matrix Precise Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,1617 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fc26bc5e546ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer I - IGEN</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf78475cc5cb677</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Redshift, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eb46efc6fde95a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Crunchyroll</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0923446b17c24fb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Developer - Used Car Marketplace</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, TensorFlow, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35887229aed27aab</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5aa92195876ba158</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Snowflake, Kafka, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer - SRE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8df970db5b7b3a83</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84efe7a83b63aa43</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c00441d38fc0fd6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=954afdc88cb5de9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SaaS Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eea102f72e51740d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0a1439f7f9e1fb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Assembly Software</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4249ab685f983fe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Ad Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Safety Modeling Engineer – Counterfactual &amp; Behavioral Safety Modeling (GPSSC)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b7d2f6c4711b0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI, Intern</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>G-P</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, spaCy, NLTK, Git, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fcef722b57cbbff</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Engagement Strategist, Marketing Applied Sciences</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a99bed4176097fbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Jenkins, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Kafka, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f7619497b7f1c5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Quality Automation Engineer (SDET) - Career</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Jenkins, Terraform, BigQuery, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Docker, GitHub Actions, Git, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17bd45ae6e7d2ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4fc304bf7f156b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3657a51114c6bef</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84af3a88e7c1674a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Capacity and Performance Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, PyTorch, BigQuery, Kubernetes, BigQuery, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c4c3043fae69d9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>26-1083: Full Stack /Python Developer - Herndon, VA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Navitas Business Consulting</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12953927f33cdfd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer I (U.S. Citizenship Required)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd5de286ff8eb5d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97dcade9e0a52740</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d640be81da9d4ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0864e7088bf1f8bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e388ca97e092639</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f003552794cd01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99cfac5454511eaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Azure Data &amp; AI Architect - Remote US</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>eGroup Enabling Technologies</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54dd88e713de4295</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43ad08d27434b10c</t>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04c3fcefd8a39bfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Self Service Automation</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bb823a6cbd6b424</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Agent Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Python, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07791b5f995cbc43</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, PySpark, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9082ad1cf497165</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a62a29222afcbb41</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior ML Infrastructure Engineer - Embodied AI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76e5e8a8069b7c11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eef9dc26eb6bcf9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91880ff78d80d51a</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Predictive Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbd989aa0dad5ef5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-30.xlsx
+++ b/daily_matches/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,77 +486,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake, Dataflow</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Data Scientist (GPSSC)</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake</t>
+          <t>AI Engineer, RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3733618642dbd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, S3, EC2, Redshift, Kinesis</t>
+          <t>AI Engineer, RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ff0b4b24920c72</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Engineer, AI Solutions</t>
+          <t>Forward-Deployed Data Scientist II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffff09002cee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6050c9d7e9e4663e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Forward-Deployed Data Scientist II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3646206d4fca8b7e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Forward-Deployed Data Scientist II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, EC2, Docker, Kubernetes, AKS</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7fc938c9d80265</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Artificial Intelligence - AI Architect</t>
+          <t>Forward-Deployed Data Scientist II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pellera Technologies</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9915fb51c50be337</t>
+          <t>https://www.indeed.com/viewjob?jk=e853103e53ab09ef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Artificial Intelligence - AI Architect</t>
+          <t>Software Engineer, Identity and Access Management</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pellera Technologies</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098a368550354f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd39762b7995bcd8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, MLflow, Apache Airflow, CI/CD, Terraform, Git, Databricks</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852eedab8ea16518</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Databricks</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, S3, EC2, CI/CD, Terraform, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf78475cc5cb677</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Software Engineer (Apps)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Redshift, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Git, Kafka, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,94 +951,94 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb46efc6fde95a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6c0fdf55419fe1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Development in Test (SDET III)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Crunchyroll</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0923446b17c24fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f788c85d6ae79fd9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=898eeb6efd9d40c8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, TensorFlow, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35887229aed27aab</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa92195876ba158</t>
+          <t>https://www.indeed.com/viewjob?jk=8391d1c18c025a89</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Product Engineer | Growth and Transformation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Snowflake, Kafka, MySQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+          <t>https://www.indeed.com/viewjob?jk=428aea251223d821</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Git, Snowflake, Databricks, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df970db5b7b3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Software Engineer II, ML Ops</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Generate Biomedicines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Copilot, Redshift, Kubernetes, CI/CD, Redshift, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84efe7a83b63aa43</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed0e8d914cf2fc3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Numa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00441d38fc0fd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f4f2ed5d680066</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Associate AWS Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Bespin Global</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, SQL</t>
+          <t>Copilot, S3, EC2, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3c6637d314836da</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fluke</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, S3, EC2, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954afdc88cb5de9b</t>
+          <t>https://www.indeed.com/viewjob?jk=de9989cbbb09da95</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SaaS Threat Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shipt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Gemini, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea102f72e51740d</t>
+          <t>https://www.indeed.com/viewjob?jk=54f9fcd23bd2eaba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a1439f7f9e1fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d22a7fc8af4ba9f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Assembly Software</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL</t>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4249ab685f983fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Safety Modeling Engineer – Counterfactual &amp; Behavioral Safety Modeling (GPSSC)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b7d2f6c4711b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b34891601e8f94ce</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI, Intern</t>
+          <t>Data Scientist - Space Intelligence</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>G-P</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, spaCy, NLTK, Git, Python</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,987 +1511,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcef722b57cbbff</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9a1c8111c1535c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Engagement Strategist, Marketing Applied Sciences</t>
+          <t>Associate Data Scientist - Space Intelligence</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a99bed4176097fbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Development Engineer III</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Jenkins, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Applied Materials</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Kafka, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7619497b7f1c5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Jenkins, Terraform, BigQuery, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, GitHub Actions, Git, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17bd45ae6e7d2ac5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fc304bf7f156b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3657a51114c6bef</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>API Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84af3a88e7c1674a</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Capacity and Performance Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, PyTorch, BigQuery, Kubernetes, BigQuery, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c4c3043fae69d9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>26-1083: Full Stack /Python Developer - Herndon, VA</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Navitas Business Consulting</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12953927f33cdfd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Software Engineer I (U.S. Citizenship Required)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Blue Yonder</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, AKS, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5de286ff8eb5d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97dcade9e0a52740</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d640be81da9d4ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0864e7088bf1f8bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e388ca97e092639</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70f003552794cd01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Docker, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99cfac5454511eaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Azure Data &amp; AI Architect - Remote US</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>eGroup Enabling Technologies</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Charleston, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54dd88e713de4295</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>USA TODAY Co.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04c3fcefd8a39bfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Self Service Automation</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb823a6cbd6b424</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AI Agent Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Python, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07791b5f995cbc43</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, PySpark, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9082ad1cf497165</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a62a29222afcbb41</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior ML Infrastructure Engineer - Embodied AI</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76e5e8a8069b7c11</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eef9dc26eb6bcf9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91880ff78d80d51a</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Predictive Analytics Specialist</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd989aa0dad5ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b88aba39c21bd34</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-30.xlsx
+++ b/daily_matches/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>LangChain, S3, Glue, Redshift, Data Lake, FastAPI, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>AI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark</t>
+          <t>AI Engineer, Data Scientist, LLaMA, Gemini, Copilot, S3, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=08d6323e8d4d4853</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward-Deployed Data Scientist II</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6050c9d7e9e4663e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3d30d5e319287f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Forward-Deployed Data Scientist II</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3646206d4fca8b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2673c495261449</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward-Deployed Data Scientist II</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Gensim, BigQuery, CI/CD, Git, BigQuery, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7fc938c9d80265</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Forward-Deployed Data Scientist II</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, XGBoost, CatBoost, Keras, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, BigQuery, CI/CD, Git, Snowflake, BigQuery, MySQL, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e853103e53ab09ef</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Identity and Access Management</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Marsh McLennan Agency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd39762b7995bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6594661d6157820</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Marketing Data Scientist, Measurement &amp; Modeling</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Fleetpride</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, BigQuery, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=529e29eaf69cc617</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect - Agentic AI &amp; Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e691105221837bb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Solution Architect - Agentic AI &amp; Data BFSI Industry</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, CI/CD, Terraform, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=1d65a3008f896bd3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer (Apps)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Git, Kafka, MySQL, MongoDB, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6c0fdf55419fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=02f1a08365eebef5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development in Test (SDET III)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Nerdio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f788c85d6ae79fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=90c972610e28a907</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Specialist Software Developer B2B Commerce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898eeb6efd9d40c8</t>
+          <t>https://www.indeed.com/viewjob?jk=83c63e4abd182019</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8028d0d5b1df65</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8391d1c18c025a89</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cdda50be7be595</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Product Engineer | Growth and Transformation</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=428aea251223d821</t>
+          <t>https://www.indeed.com/viewjob?jk=c871627a5fbd7d46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, Git, Snowflake, Databricks, Tableau, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=129e7c3974efc5f3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II, ML Ops</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Generate Biomedicines</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Redshift, Kubernetes, CI/CD, Redshift, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed0e8d914cf2fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed8aea93c76f0472</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Numa</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f4f2ed5d680066</t>
+          <t>https://www.indeed.com/viewjob?jk=7559827bdb57a0fb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate AWS Cloud Migration Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bespin Global</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3c6637d314836da</t>
+          <t>https://www.indeed.com/viewjob?jk=74277bcbbe107636</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9989cbbb09da95</t>
+          <t>https://www.indeed.com/viewjob?jk=12cae2ae25e8b014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shipt</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gemini, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f9fcd23bd2eaba</t>
+          <t>https://www.indeed.com/viewjob?jk=6306faf8c94f493a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>K Health</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22a7fc8af4ba9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0abbf2db2329d7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=fddf6b2cd77b36d0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=6232b3c854695d12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34891601e8f94ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2acdbfef72fe8382</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist - Space Intelligence</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,42 +1511,1827 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9a1c8111c1535c</t>
+          <t>https://www.indeed.com/viewjob?jk=667feb24362ea298</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Scientist - Space Intelligence</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fargo, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd95cb5f129ba4a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27fe3748b4c6e9ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96e55f69edf8e710</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Newport, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f877d29517d1e8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hudson, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=578051612c793f74</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2a751d1b4654154</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=720d2d19c637dbd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d3ec8a3acdaf608</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bcde40daa1b5a67</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b19225c5d43f5354</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9eda53066f047cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d2b852deb59b35a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dayton, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ebd8c576a7f84b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c43ffb9dc8728db</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Derby, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0deee98ca536f71b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48cbf9152cf68ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c245b04f72dbcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Clinton, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c0ae7ba24ecce9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Watson, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=937b2de1fa924199</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fb756925d51a6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tyler, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=589226c2de6af70c</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1721b2eddbb95215</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Stafford, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85f8c3b8c340ef19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e411377c0061c4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=193365b70ef7abc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fb5e93fe4c3b2ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Parlin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b8a979d87a9e8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8adc97440a91f562</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Medway, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5260f1234c40edbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2191c8bc4701830</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c6b9c845547786b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Great American Insurance Group</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26f70104d9111875</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467517a4a9d5a827</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0656c0ad796ae71d</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Consultant Analytical Engineer Expanse</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Redshift, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=876ab4f30e6dcf55</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer | Infrastructure | Government</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gecko Robotics</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec38365c22e7be8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer | Infrastructure | Government</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Gecko Robotics</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c66812735b42a64</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c14f672c98afd19d</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Pittsford, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b0e815fda68f793</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Analyst - Finance Technology</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Victaulic</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abbc07673832f61b</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LocaliQ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0532bb0b7078fc32</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8807311fbfef226d</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5822dcce000fd7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LocaliQ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b312af6879027a5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, Git, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7ff5bddbfce18c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer | Infrastructure</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Gecko Robotics</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c73f48532742c596</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Test &amp; Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gecko Robotics</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab89f9b47f06f813</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer | Infrastructure</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gecko Robotics</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90eedf854f2d5865</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AI NATIVE SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=435439b76755400f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI/ML Developer II (Remote)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>The Home Depot</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D82" t="n">
         <v>10</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b88aba39c21bd34</t>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>BigQuery, CI/CD, Git, BigQuery, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Information Technology (IT) Intern (AI and ITSM) - Remote</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Apotheco Pharmacy Group</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Short Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db7eebf6d7758930</t>
         </is>
       </c>
     </row>
